--- a/游戏设计王/捕鱼游戏数学-PartII-特殊炮模型.xlsx
+++ b/游戏设计王/捕鱼游戏数学-PartII-特殊炮模型.xlsx
@@ -301,12 +301,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000%"/>
+    <numFmt numFmtId="177" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1008,7 +1009,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1084,6 +1085,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1785,7 +1789,7 @@
       <c r="B6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="44">
         <f>IF(OR(C4="",C5=""),"",C4-C5)</f>
         <v>0.2</v>
       </c>
@@ -1838,7 +1842,7 @@
       <c r="B8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="45">
         <f>IF(OR(C5="",C7="",C7=0),"",C5/C7)</f>
         <v>0.007</v>
       </c>
@@ -1891,7 +1895,7 @@
       <c r="B10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="45">
         <f>IF(OR(C6="",C9="",C9=0),"",C6/C9)</f>
         <v>0.001</v>
       </c>
@@ -1918,7 +1922,7 @@
       <c r="B11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="44">
         <f>IF(OR(C10="",C8="",C8=0),"",C10/C8)</f>
         <v>0.142857142857143</v>
       </c>
@@ -2071,7 +2075,7 @@
       <c r="C17" s="12">
         <v>100</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="44">
         <f>IF(OR(C17="",C17=0,$C$15="",$C$15=0),"",$C$14/(C17*$C$15))</f>
         <v>0.666666666666667</v>
       </c>
@@ -2079,7 +2083,7 @@
         <f>IF(OR(D17="",C17=""),"",C17*D17)</f>
         <v>66.6666666666667</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="44">
         <f t="shared" ref="F17:F22" si="0">IF(OR(E17="",$C$14="",$C$14=0),"",E17/$C$14)</f>
         <v>0.333333333333333</v>
       </c>
@@ -2100,7 +2104,7 @@
       <c r="C18" s="12">
         <v>100</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="44">
         <f>IF(OR(C18="",C18=0,$C$15="",$C$15=0),"",$C$14/(C18*$C$15))</f>
         <v>0.666666666666667</v>
       </c>
@@ -2108,7 +2112,7 @@
         <f>IF(OR(D18="",C18=""),"",C18*D18)</f>
         <v>66.6666666666667</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="44">
         <f t="shared" si="0"/>
         <v>0.333333333333333</v>
       </c>
@@ -2129,7 +2133,7 @@
       <c r="C19" s="12">
         <v>100</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="44">
         <f>IF(OR(C19="",C19=0,$C$15="",$C$15=0),"",$C$14/(C19*$C$15))</f>
         <v>0.666666666666667</v>
       </c>
@@ -2137,7 +2141,7 @@
         <f>IF(OR(D19="",C19=""),"",C19*D19)</f>
         <v>66.6666666666667</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="44">
         <f t="shared" si="0"/>
         <v>0.333333333333333</v>
       </c>
@@ -2156,7 +2160,7 @@
         <v>64</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="11" t="str">
+      <c r="D20" s="44" t="str">
         <f>IF(OR(C20="",C20=0,$C$15="",$C$15=0),"",$C$14/(C20*$C$15))</f>
         <v/>
       </c>
@@ -2164,7 +2168,7 @@
         <f>IF(OR(D20="",C20=""),"",C20*D20)</f>
         <v/>
       </c>
-      <c r="F20" s="11" t="str">
+      <c r="F20" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2183,7 +2187,7 @@
         <v>65</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="11" t="str">
+      <c r="D21" s="44" t="str">
         <f>IF(OR(C21="",C21=0,$C$15="",$C$15=0),"",$C$14/(C21*$C$15))</f>
         <v/>
       </c>
@@ -2191,7 +2195,7 @@
         <f>IF(OR(D21="",C21=""),"",C21*D21)</f>
         <v/>
       </c>
-      <c r="F21" s="11" t="str">
+      <c r="F21" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2219,7 +2223,7 @@
         <f>SUM(E17:E21)</f>
         <v>200</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="44">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
